--- a/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura de Caja" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre de Caja" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Registro Mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura de Caja" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre de Caja" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Mensual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Area">'Instrucciones'!$A$1:$A$20</definedName>
-    <definedName localSheetId="1" name="_xlnm.Print_Area">'Apertura de Caja'!$A$1:$F$18</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Cierre de Caja'!$A$1:$F$48</definedName>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Registro Mensual'!$A$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura de Caja'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre de Caja'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Registro Mensual'!$A$1:$I$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,9 +25,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -99,6 +99,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -138,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -193,87 +198,110 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="27">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="2" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="3" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="5" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="5" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -633,122 +661,131 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="80"/>
+    <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="30" r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Kit de Tareas — Dark Kitchen</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="25" r="3">
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Checklist de Apertura y Cierre de Caja</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="35" r="5">
+    <row r="4"/>
+    <row r="5" ht="35" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>📋 Instrucciones de Uso</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
           <t>5. Añade o elimina filas según tu operativa diaria.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
           <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
           <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="5" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>© AI Chef Pro — aichef.pro</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>29 años de experiencia en alta hostelería · 15 años de consultoría gastronómica</t>
-        </is>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="18">
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -756,7 +793,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -770,22 +816,22 @@
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Apertura de Caja — Dark Kitchen</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -797,8 +843,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -830,7 +876,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -844,7 +890,7 @@
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -858,7 +904,7 @@
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -872,7 +918,7 @@
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -886,7 +932,7 @@
       <c r="E8" s="10" t="inlineStr"/>
       <c r="F8" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -900,7 +946,7 @@
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -914,7 +960,7 @@
       <c r="E10" s="10" t="inlineStr"/>
       <c r="F10" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -928,7 +974,7 @@
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -942,7 +988,7 @@
       <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -956,7 +1002,7 @@
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -970,7 +1016,7 @@
       <c r="E14" s="10" t="inlineStr"/>
       <c r="F14" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -984,7 +1030,27 @@
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="30" r="17">
+    <row r="16">
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(D5:D15,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora: ________</t>
@@ -1006,13 +1072,18 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="D2:F2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:F15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15" type="list">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1026,22 +1097,22 @@
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="25"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cierre de Caja — Dark Kitchen</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Fecha: ____/____/________</t>
@@ -1053,8 +1124,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>#</t>
@@ -1086,7 +1157,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="5">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="8" t="n">
         <v>1</v>
       </c>
@@ -1100,7 +1171,7 @@
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="6">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="10" t="n">
         <v>2</v>
       </c>
@@ -1114,7 +1185,7 @@
       <c r="E6" s="10" t="inlineStr"/>
       <c r="F6" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="7">
+    <row r="7" ht="24" customHeight="1">
       <c r="A7" s="8" t="n">
         <v>3</v>
       </c>
@@ -1128,7 +1199,7 @@
       <c r="E7" s="8" t="inlineStr"/>
       <c r="F7" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="8">
+    <row r="8" ht="24" customHeight="1">
       <c r="A8" s="10" t="n">
         <v>4</v>
       </c>
@@ -1142,7 +1213,7 @@
       <c r="E8" s="10" t="inlineStr"/>
       <c r="F8" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="9">
+    <row r="9" ht="24" customHeight="1">
       <c r="A9" s="8" t="n">
         <v>5</v>
       </c>
@@ -1156,7 +1227,7 @@
       <c r="E9" s="8" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="A10" s="10" t="n">
         <v>6</v>
       </c>
@@ -1170,7 +1241,7 @@
       <c r="E10" s="10" t="inlineStr"/>
       <c r="F10" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="11">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
@@ -1184,7 +1255,7 @@
       <c r="E11" s="8" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="12">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="10" t="n">
         <v>8</v>
       </c>
@@ -1198,7 +1269,7 @@
       <c r="E12" s="10" t="inlineStr"/>
       <c r="F12" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="13">
+    <row r="13" ht="24" customHeight="1">
       <c r="A13" s="8" t="n">
         <v>9</v>
       </c>
@@ -1212,7 +1283,7 @@
       <c r="E13" s="8" t="inlineStr"/>
       <c r="F13" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
@@ -1226,7 +1297,7 @@
       <c r="E14" s="10" t="inlineStr"/>
       <c r="F14" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="15">
+    <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="n">
         <v>11</v>
       </c>
@@ -1240,7 +1311,7 @@
       <c r="E15" s="8" t="inlineStr"/>
       <c r="F15" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="24" r="16">
+    <row r="16" ht="24" customHeight="1">
       <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
@@ -1254,14 +1325,34 @@
       <c r="E16" s="10" t="inlineStr"/>
       <c r="F16" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="32" r="18">
+    <row r="17">
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C17">
+        <f>COUNTIF(D5:D16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E17">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
         <is>
           <t>💰 Recuento de Efectivo por Denominación</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="26" r="19">
+    <row r="19" ht="26" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Denominación</t>
@@ -1278,14 +1369,16 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="20">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" s="14" t="inlineStr">
         <is>
           <t>BILLETES</t>
         </is>
       </c>
-    </row>
-    <row customHeight="1" ht="22" r="21">
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
           <t>500 €</t>
@@ -1296,10 +1389,10 @@
       </c>
       <c r="C21" s="16">
         <f>B21*500</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="inlineStr">
         <is>
           <t>200 €</t>
@@ -1310,10 +1403,10 @@
       </c>
       <c r="C22" s="18">
         <f>B22*200</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="23">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
           <t>100 €</t>
@@ -1324,10 +1417,10 @@
       </c>
       <c r="C23" s="16">
         <f>B23*100</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="24">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>50 €</t>
@@ -1338,10 +1431,10 @@
       </c>
       <c r="C24" s="18">
         <f>B24*50</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="25">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
         <is>
           <t>20 €</t>
@@ -1352,10 +1445,10 @@
       </c>
       <c r="C25" s="16">
         <f>B25*20</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="26">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
           <t>10 €</t>
@@ -1366,10 +1459,10 @@
       </c>
       <c r="C26" s="18">
         <f>B26*10</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="27">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
         <is>
           <t>5 €</t>
@@ -1380,17 +1473,19 @@
       </c>
       <c r="C27" s="16">
         <f>B27*5</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="24" r="28">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
       <c r="A28" s="14" t="inlineStr">
         <is>
           <t>MONEDAS</t>
         </is>
       </c>
-    </row>
-    <row customHeight="1" ht="22" r="29">
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
         <is>
           <t>2 €</t>
@@ -1401,10 +1496,10 @@
       </c>
       <c r="C29" s="16">
         <f>B29*2</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="30">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
           <t>1 €</t>
@@ -1415,10 +1510,10 @@
       </c>
       <c r="C30" s="18">
         <f>B30*1</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="31">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
         <is>
           <t>0,50 €</t>
@@ -1429,10 +1524,10 @@
       </c>
       <c r="C31" s="16">
         <f>B31*0.5</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="32">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
           <t>0,20 €</t>
@@ -1443,10 +1538,10 @@
       </c>
       <c r="C32" s="18">
         <f>B32*0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="33">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
         <is>
           <t>0,10 €</t>
@@ -1457,10 +1552,10 @@
       </c>
       <c r="C33" s="16">
         <f>B33*0.1</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="34">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
           <t>0,05 €</t>
@@ -1471,10 +1566,10 @@
       </c>
       <c r="C34" s="18">
         <f>B34*0.05</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="22" r="35">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
         <is>
           <t>0,01 €</t>
@@ -1485,10 +1580,10 @@
       </c>
       <c r="C35" s="16">
         <f>B35*0.01</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="28" r="36">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
           <t>TOTAL EFECTIVO</t>
@@ -1497,17 +1592,18 @@
       <c r="B36" s="20" t="n"/>
       <c r="C36" s="21">
         <f>SUM(C21:C35)</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="30" r="38">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
         <is>
           <t>📊 Resumen de Cierre</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="26" r="39">
+    <row r="39" ht="26" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Concepto</t>
@@ -1519,7 +1615,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="40">
+    <row r="40" ht="24" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Total Efectivo</t>
@@ -1527,10 +1623,10 @@
       </c>
       <c r="B40" s="16">
         <f>C36</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="24" r="41">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>Total Tarjetas (Visa/MC)</t>
@@ -1540,7 +1636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="42">
+    <row r="42" ht="24" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Total Otros (Bizum, Vales)</t>
@@ -1550,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="43">
+    <row r="43" ht="24" customHeight="1">
       <c r="A43" s="22" t="inlineStr">
         <is>
           <t>TOTAL FACTURADO</t>
@@ -1558,10 +1654,10 @@
       </c>
       <c r="B43" s="23">
         <f>B40+B41+B42</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="24" r="44">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Z del TPV</t>
@@ -1571,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row customHeight="1" ht="24" r="45">
+    <row r="45" ht="24" customHeight="1">
       <c r="A45" s="22" t="inlineStr">
         <is>
           <t>DESCUADRE</t>
@@ -1579,10 +1675,11 @@
       </c>
       <c r="B45" s="23">
         <f>B43-B44</f>
-        <v/>
-      </c>
-    </row>
-    <row customHeight="1" ht="30" r="47">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora: ________</t>
@@ -1609,13 +1706,18 @@
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:F16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$D5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Selecciona ✓, ✗ o —" errorTitle="Valor no válido" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16" type="list">
+    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1629,25 +1731,25 @@
   <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="12"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="16"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="16"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row customHeight="1" ht="40" r="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Registro Mensual de Caja — Dark Kitchen</t>
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="28" r="2">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Mes: ________________     Año: ________</t>
@@ -1659,8 +1761,8 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="8" r="3"/>
-    <row customHeight="1" ht="28" r="4">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Fecha</t>
@@ -1707,7 +1809,7 @@
         </is>
       </c>
     </row>
-    <row customHeight="1" ht="22" r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
@@ -1725,7 +1827,7 @@
       </c>
       <c r="F5" s="16">
         <f>C5+D5+E5</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G5" s="16" t="inlineStr"/>
       <c r="H5" s="16" t="n">
@@ -1733,7 +1835,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
@@ -1751,7 +1853,7 @@
       </c>
       <c r="F6" s="18">
         <f>C6+D6+E6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G6" s="18" t="inlineStr"/>
       <c r="H6" s="18" t="n">
@@ -1759,7 +1861,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
@@ -1777,7 +1879,7 @@
       </c>
       <c r="F7" s="16">
         <f>C7+D7+E7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G7" s="16" t="inlineStr"/>
       <c r="H7" s="16" t="n">
@@ -1785,7 +1887,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="17" t="n">
         <v>4</v>
       </c>
@@ -1803,7 +1905,7 @@
       </c>
       <c r="F8" s="18">
         <f>C8+D8+E8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G8" s="18" t="inlineStr"/>
       <c r="H8" s="18" t="n">
@@ -1811,7 +1913,7 @@
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
@@ -1829,7 +1931,7 @@
       </c>
       <c r="F9" s="16">
         <f>C9+D9+E9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G9" s="16" t="inlineStr"/>
       <c r="H9" s="16" t="n">
@@ -1837,7 +1939,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="10">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
@@ -1855,7 +1957,7 @@
       </c>
       <c r="F10" s="18">
         <f>C10+D10+E10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G10" s="18" t="inlineStr"/>
       <c r="H10" s="18" t="n">
@@ -1863,7 +1965,7 @@
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="11">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
@@ -1881,7 +1983,7 @@
       </c>
       <c r="F11" s="16">
         <f>C11+D11+E11</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G11" s="16" t="inlineStr"/>
       <c r="H11" s="16" t="n">
@@ -1889,7 +1991,7 @@
       </c>
       <c r="I11" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="12">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
@@ -1907,7 +2009,7 @@
       </c>
       <c r="F12" s="18">
         <f>C12+D12+E12</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G12" s="18" t="inlineStr"/>
       <c r="H12" s="18" t="n">
@@ -1915,7 +2017,7 @@
       </c>
       <c r="I12" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="13">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
@@ -1933,7 +2035,7 @@
       </c>
       <c r="F13" s="16">
         <f>C13+D13+E13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G13" s="16" t="inlineStr"/>
       <c r="H13" s="16" t="n">
@@ -1941,7 +2043,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="14">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>10</v>
       </c>
@@ -1959,7 +2061,7 @@
       </c>
       <c r="F14" s="18">
         <f>C14+D14+E14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G14" s="18" t="inlineStr"/>
       <c r="H14" s="18" t="n">
@@ -1967,7 +2069,7 @@
       </c>
       <c r="I14" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="15">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
@@ -1985,7 +2087,7 @@
       </c>
       <c r="F15" s="16">
         <f>C15+D15+E15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G15" s="16" t="inlineStr"/>
       <c r="H15" s="16" t="n">
@@ -1993,7 +2095,7 @@
       </c>
       <c r="I15" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="16">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="n">
         <v>12</v>
       </c>
@@ -2011,7 +2113,7 @@
       </c>
       <c r="F16" s="18">
         <f>C16+D16+E16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G16" s="18" t="inlineStr"/>
       <c r="H16" s="18" t="n">
@@ -2019,7 +2121,7 @@
       </c>
       <c r="I16" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="17">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
@@ -2037,7 +2139,7 @@
       </c>
       <c r="F17" s="16">
         <f>C17+D17+E17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G17" s="16" t="inlineStr"/>
       <c r="H17" s="16" t="n">
@@ -2045,7 +2147,7 @@
       </c>
       <c r="I17" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="18">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="17" t="n">
         <v>14</v>
       </c>
@@ -2063,7 +2165,7 @@
       </c>
       <c r="F18" s="18">
         <f>C18+D18+E18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G18" s="18" t="inlineStr"/>
       <c r="H18" s="18" t="n">
@@ -2071,7 +2173,7 @@
       </c>
       <c r="I18" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="19">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
@@ -2089,7 +2191,7 @@
       </c>
       <c r="F19" s="16">
         <f>C19+D19+E19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G19" s="16" t="inlineStr"/>
       <c r="H19" s="16" t="n">
@@ -2097,7 +2199,7 @@
       </c>
       <c r="I19" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="20">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="n">
         <v>16</v>
       </c>
@@ -2115,7 +2217,7 @@
       </c>
       <c r="F20" s="18">
         <f>C20+D20+E20</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G20" s="18" t="inlineStr"/>
       <c r="H20" s="18" t="n">
@@ -2123,7 +2225,7 @@
       </c>
       <c r="I20" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="21">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
@@ -2141,7 +2243,7 @@
       </c>
       <c r="F21" s="16">
         <f>C21+D21+E21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G21" s="16" t="inlineStr"/>
       <c r="H21" s="16" t="n">
@@ -2149,7 +2251,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="22">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>18</v>
       </c>
@@ -2167,7 +2269,7 @@
       </c>
       <c r="F22" s="18">
         <f>C22+D22+E22</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G22" s="18" t="inlineStr"/>
       <c r="H22" s="18" t="n">
@@ -2175,7 +2277,7 @@
       </c>
       <c r="I22" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="23">
+    <row r="23" ht="22" customHeight="1">
       <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
@@ -2193,7 +2295,7 @@
       </c>
       <c r="F23" s="16">
         <f>C23+D23+E23</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G23" s="16" t="inlineStr"/>
       <c r="H23" s="16" t="n">
@@ -2201,7 +2303,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="24">
+    <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="n">
         <v>20</v>
       </c>
@@ -2219,7 +2321,7 @@
       </c>
       <c r="F24" s="18">
         <f>C24+D24+E24</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G24" s="18" t="inlineStr"/>
       <c r="H24" s="18" t="n">
@@ -2227,7 +2329,7 @@
       </c>
       <c r="I24" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="25">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
@@ -2245,7 +2347,7 @@
       </c>
       <c r="F25" s="16">
         <f>C25+D25+E25</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G25" s="16" t="inlineStr"/>
       <c r="H25" s="16" t="n">
@@ -2253,7 +2355,7 @@
       </c>
       <c r="I25" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="26">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="n">
         <v>22</v>
       </c>
@@ -2271,7 +2373,7 @@
       </c>
       <c r="F26" s="18">
         <f>C26+D26+E26</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G26" s="18" t="inlineStr"/>
       <c r="H26" s="18" t="n">
@@ -2279,7 +2381,7 @@
       </c>
       <c r="I26" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="27">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
@@ -2297,7 +2399,7 @@
       </c>
       <c r="F27" s="16">
         <f>C27+D27+E27</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G27" s="16" t="inlineStr"/>
       <c r="H27" s="16" t="n">
@@ -2305,7 +2407,7 @@
       </c>
       <c r="I27" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="28">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="n">
         <v>24</v>
       </c>
@@ -2323,7 +2425,7 @@
       </c>
       <c r="F28" s="18">
         <f>C28+D28+E28</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G28" s="18" t="inlineStr"/>
       <c r="H28" s="18" t="n">
@@ -2331,7 +2433,7 @@
       </c>
       <c r="I28" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="29">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="15" t="n">
         <v>25</v>
       </c>
@@ -2349,7 +2451,7 @@
       </c>
       <c r="F29" s="16">
         <f>C29+D29+E29</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G29" s="16" t="inlineStr"/>
       <c r="H29" s="16" t="n">
@@ -2357,7 +2459,7 @@
       </c>
       <c r="I29" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="30">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="n">
         <v>26</v>
       </c>
@@ -2375,7 +2477,7 @@
       </c>
       <c r="F30" s="18">
         <f>C30+D30+E30</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G30" s="18" t="inlineStr"/>
       <c r="H30" s="18" t="n">
@@ -2383,7 +2485,7 @@
       </c>
       <c r="I30" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="31">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="15" t="n">
         <v>27</v>
       </c>
@@ -2401,7 +2503,7 @@
       </c>
       <c r="F31" s="16">
         <f>C31+D31+E31</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G31" s="16" t="inlineStr"/>
       <c r="H31" s="16" t="n">
@@ -2409,7 +2511,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="32">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="n">
         <v>28</v>
       </c>
@@ -2427,7 +2529,7 @@
       </c>
       <c r="F32" s="18">
         <f>C32+D32+E32</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G32" s="18" t="inlineStr"/>
       <c r="H32" s="18" t="n">
@@ -2435,7 +2537,7 @@
       </c>
       <c r="I32" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="33">
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" s="15" t="n">
         <v>29</v>
       </c>
@@ -2453,7 +2555,7 @@
       </c>
       <c r="F33" s="16">
         <f>C33+D33+E33</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G33" s="16" t="inlineStr"/>
       <c r="H33" s="16" t="n">
@@ -2461,7 +2563,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="34">
+    <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="n">
         <v>30</v>
       </c>
@@ -2479,7 +2581,7 @@
       </c>
       <c r="F34" s="18">
         <f>C34+D34+E34</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G34" s="18" t="inlineStr"/>
       <c r="H34" s="18" t="n">
@@ -2487,7 +2589,7 @@
       </c>
       <c r="I34" s="10" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="22" r="35">
+    <row r="35" ht="22" customHeight="1">
       <c r="A35" s="15" t="n">
         <v>31</v>
       </c>
@@ -2505,7 +2607,7 @@
       </c>
       <c r="F35" s="16">
         <f>C35+D35+E35</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G35" s="16" t="inlineStr"/>
       <c r="H35" s="16" t="n">
@@ -2513,7 +2615,7 @@
       </c>
       <c r="I35" s="8" t="inlineStr"/>
     </row>
-    <row customHeight="1" ht="28" r="36">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
         <is>
           <t>TOTALES</t>
@@ -2521,34 +2623,35 @@
       </c>
       <c r="B36" s="24">
         <f>SUM(B5:B35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C36" s="24">
         <f>SUM(C5:C35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D36" s="24">
         <f>SUM(D5:D35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E36" s="24">
         <f>SUM(E5:E35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="F36" s="24">
         <f>SUM(F5:F35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="G36" s="24">
         <f>SUM(G5:G35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="H36" s="24">
         <f>SUM(H5:H35)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="I36" s="19" t="inlineStr"/>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
@@ -2563,7 +2666,7 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup fitToHeight="0" fitToWidth="1" orientation="landscape" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
@@ -14,8 +14,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura de Caja'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura de Caja'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre de Caja'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre de Caja'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Registro Mensual'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Registro Mensual'!$A$1:$I$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,7 +814,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1082,8 +1085,16 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1092,7 +1103,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1716,8 +1727,16 @@
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1726,7 +1745,7 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2666,7 +2685,15 @@
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
+++ b/astro-site/public/dl/kit-tareas-dark-kitchen/09-apertura-cierre-caja.xlsx
@@ -13,13 +13,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro Mensual" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura de Caja'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura de Caja'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Apertura de Caja'!$A$1:$G$26</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre de Caja'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre de Caja'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Cierre de Caja'!$A$1:$G$57</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Registro Mensual'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Registro Mensual'!$A$1:$I$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Registro Mensual'!$A$1:$J$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,8 +107,26 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -143,6 +161,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F5F5"/>
         <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -216,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,16 +323,96 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C8E6C9"/>
           <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF3CD"/>
+          <bgColor rgb="00FFF3CD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -666,136 +779,295 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Kit de Tareas — Dark Kitchen</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Checklist de Apertura y Cierre de Caja</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5" ht="35" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>📋 Instrucciones de Uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1. Este archivo contiene checklists profesionales para la apertura y cierre de tu negocio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2. Imprime las hojas que necesites o úsalas en formato digital (tablet/ordenador).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>3. Cada checklist incluye columnas para marcar tareas completadas, responsable, hora y notas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>4. Personaliza las tareas según las necesidades específicas de tu establecimiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>5. Añade o elimina filas según tu operativa diaria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>6. Usa la validación de datos en la columna '✓ Completada' para marcar el estado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>7. Rellena la firma y fecha cada día para mantener el control.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>💡 Consejo: Plastifica una copia impresa y usa rotuladores borrables para reutilizarla cada día.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="27" t="inlineStr">
+        <is>
+          <t>Apertura y Cierre de Caja — Dark Kitchen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>Qué resuelve</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>▸ El arqueo diario: fondo de caja, recuento del cajón por denominaciones, Z del TPV y descuadre — y el registro mensual para ver de un vistazo qué días no cuadraron.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
+          <t>Cómo usar — Apertura de Caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>▸ Cuenta el fondo y escribe el importe en la celda VERDE «Fondo de caja inicial (€)». De ahí lo lee el cierre: no hay que volver a teclearlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Cómo usar — Cierre de Caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>▸ En «Recuento de Efectivo por Denominación» rellena SOLO la columna «Cantidad» (número de billetes o monedas, entero): el subtotal y el TOTAL EFECTIVO se calculan solos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>▸ En el «Resumen de Cierre» sólo escribes tres cifras: Total Tarjetas, Total Otros y la Z del TPV. Lo demás es fórmula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>▸ El fondo se descuenta solo: TOTAL FACTURADO = (efectivo contado − fondo) + tarjetas + otros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>▸ DESCUADRE = TOTAL FACTURADO − Z del TPV. Si la casilla se pone ÁMBAR, la caja no cuadra: revísalo ANTES de firmar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Registro Mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>▸ Una fila por día: escribe fondo, ventas por medio de pago, Z del TPV y depósito; el Total Facturado y el Descuadre se calculan solos y el descuadre se pone ámbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>▸ El fondo de caja es un saldo, no una venta: la fila TOTALES muestra el fondo MEDIO de los días anotados, no su suma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>Celdas editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>▸ Todo lo que se rellena a diario va en VERDE: Responsable, Hora Límite, ✓ Completada, Firma, Notas, las cantidades del recuento y los importes del resumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>Cómo cuenta el contador</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>▸ Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>▸ «N/A» = no aplica en tu local: esa tarea SALE del total (no la borres, márcala N/A). «—» = no hecha: sigue contando como pendiente y baja el porcentaje, que es de lo que se trata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>▸ El denominador cuenta las tareas escritas en la columna «Tarea», no un número fijo: si añades o borras tareas, el total se ajusta solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="28" t="inlineStr">
+        <is>
+          <t>Filas libres</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="B36" s="29" t="inlineStr">
+        <is>
+          <t>▸ Al final de cada tabla hay 5 filas verdes libres DENTRO del rango que cuenta el contador: escribe ahí tus tareas propias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="B37" s="29" t="inlineStr">
+        <is>
+          <t>▸ Si necesitas más, inserta filas DENTRO de la tabla (clic derecho → Insertar), nunca por debajo de la última: lo que se escriba fuera del rango no lo cuenta nadie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Protección de la hoja</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="B41" s="29" t="inlineStr">
+        <is>
+          <t>▸ Las hojas con fórmulas van protegidas SIN contraseña: las celdas de entrada (las verdes) están desbloqueadas y los cálculos no se pisan por accidente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>▸ Puedes insertar y borrar filas con la protección puesta. Para cambiar la estructura: Revisar → Desproteger hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Se conecta con</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="B46" s="29" t="inlineStr">
+        <is>
+          <t>▸ 08-apertura-cierre-negocio.xlsx — checklist del LOCAL completo: es el MARCO del día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="B47" s="29" t="inlineStr">
+        <is>
+          <t>▸ 01-apertura-cierre.xlsx — el mismo día con el DETALLE por área (cocina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>▸ 09-apertura-cierre-caja.xlsx — la CAJA: fondo, recuento por denominaciones, Z del TPV y descuadre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
+      <c r="B49" s="29" t="inlineStr">
+        <is>
+          <t>▸ Orden de uso: local → áreas → caja. Cada fichero cubre un nivel: el de negocio marca el HITO (encender, abrir, cerrar), el de áreas detalla CÓMO se hace en cada zona y el de caja lleva el DINERO. Si una tarea aparece en dos, es a propósito: una es el hito y la otra el detalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
+      <c r="B50" s="29" t="inlineStr">
+        <is>
+          <t>▸ Estás en 09-apertura-cierre-caja.xlsx: esta es la CAJA — el DINERO del día (fondo, recuento, Z del TPV y descuadre); el marco del día está en 08-apertura-cierre-negocio.xlsx y el detalle por zona, en 01-apertura-cierre.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="35" customHeight="1">
+      <c r="B54" s="28" t="inlineStr">
         <is>
           <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="55" ht="18" customHeight="1">
+      <c r="B55" s="28" t="inlineStr">
         <is>
           <t>Contacto: info@aichef.pro</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
+    <row r="57" ht="18" customHeight="1">
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-dark-kitchen · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1"/>
-  </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -816,15 +1088,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -865,228 +1138,399 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>Hora Límite</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>✓ Completada</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
+          <t>Firma</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Verificar fondo de caja del día anterior</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Contar fondo de caja inicial</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Registrar importe de fondo de caja en hoja</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Anotar el fondo de caja en la celda verde de abajo</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Verificar cambio suficiente (monedas, billetes pequeños)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Encender TPV / POS</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Comprobar que el TPV está encendido y abrir turno de caja</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>Imprimir X de apertura (informe de inicio)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr"/>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Comprobar rollo de papel de ticket</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Verificar datáfono operativo</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Verificar conexión de pasarela de pago</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Anotar incidencias del turno anterior</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Firma del responsable de apertura</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="25" t="inlineStr">
+      <c r="A16" s="32" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
+      <c r="E16" s="32" t="n"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
-        <f>COUNTIF(D5:D15,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C22">
+        <f>COUNTIFS(B5:B20,"?*",E5:E20,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B15,"?*")</f>
+      <c r="E22">
+        <f>COUNTIF(B5:B20,"?*")-COUNTIF(E5:E20,"N/A")</f>
         <v>11.0</v>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fondo de caja inicial (€)</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Se descuenta del efectivo en el Cierre de Caja</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora: ________</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A17:F17"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F15">
+  <conditionalFormatting sqref="A5:G20">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$D5="✓"</formula>
+      <formula>$E5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
@@ -1105,15 +1549,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1154,581 +1599,808 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>Cuándo</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>✓ Completada</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Hora</t>
-        </is>
-      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
+          <t>Firma</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Imprimir Z de cierre (informe final del día)</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="32" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Recuento de efectivo por denominación (ver tabla inferior)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
         <is>
           <t>Calcular total efectivo</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Anotar total tarjetas (Visa/Mastercard)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr"/>
-      <c r="D8" s="10" t="inlineStr"/>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Anotar otros medios (Bizum, vales, invitaciones)</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr"/>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Total facturado = efectivo + tarjetas + otros</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr"/>
-      <c r="D10" s="10" t="inlineStr"/>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Total facturado = efectivo contado − fondo + tarjetas + otros</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr"/>
+      <c r="F10" s="32" t="n"/>
+      <c r="G10" s="32" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>Comparar con Z del TPV → calcular diferencia/descuadre</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
-      <c r="D11" s="8" t="inlineStr"/>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Registrar devoluciones del día</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr"/>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="32" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="30" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Registrar anulaciones del día</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
-      <c r="D13" s="8" t="inlineStr"/>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr"/>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>Separar fondo de caja para mañana</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr"/>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="n">
+      <c r="A15" s="30" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="31" t="inlineStr">
         <is>
           <t>Preparar depósito bancario / guardar en caja fuerte</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr"/>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>Firma del responsable de cierre</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Responsable de caja</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>Cierre</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr"/>
+      <c r="F16" s="32" t="n"/>
+      <c r="G16" s="32" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="32" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="32" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+      <c r="E18" s="32" t="n"/>
+      <c r="F18" s="32" t="n"/>
+      <c r="G18" s="32" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="n"/>
+      <c r="B20" s="35" t="n"/>
+      <c r="C20" s="32" t="n"/>
+      <c r="D20" s="32" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="32" t="n"/>
+      <c r="G20" s="32" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="n"/>
+      <c r="B21" s="35" t="n"/>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="32" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C17">
-        <f>COUNTIF(D5:D16,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C23">
+        <f>COUNTIFS(B5:B21,"?*",E5:E21,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E17">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="E23">
+        <f>COUNTIF(B5:B21,"?*")-COUNTIF(E5:E21,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>💰 Recuento de Efectivo por Denominación</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Denominación</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>Subtotal (€)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>BILLETES</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="20" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="37" t="inlineStr">
         <is>
           <t>500 €</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="16">
-        <f>B21*500</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="B27" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="39">
+        <f>B27*500</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
         <is>
           <t>200 €</t>
         </is>
       </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="18">
-        <f>B22*200</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B28" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="41">
+        <f>B28*200</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>100 €</t>
         </is>
       </c>
-      <c r="B23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="16">
-        <f>B23*100</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="B29" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="39">
+        <f>B29*100</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>50 €</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="18">
-        <f>B24*50</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="B30" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="41">
+        <f>B30*50</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="37" t="inlineStr">
         <is>
           <t>20 €</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="16">
-        <f>B25*20</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="B31" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="39">
+        <f>B31*20</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="40" t="inlineStr">
         <is>
           <t>10 €</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="18">
-        <f>B26*10</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="B32" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="41">
+        <f>B32*10</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="37" t="inlineStr">
         <is>
           <t>5 €</t>
         </is>
       </c>
-      <c r="B27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="16">
-        <f>B27*5</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="B33" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="39">
+        <f>B33*5</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>MONEDAS</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n"/>
-      <c r="C28" s="20" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="20" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>2 €</t>
         </is>
       </c>
-      <c r="B29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="16">
-        <f>B29*2</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="B35" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="39">
+        <f>B35*2</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="40" t="inlineStr">
         <is>
           <t>1 €</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="18">
-        <f>B30*1</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B36" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="41">
+        <f>B36*1</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>0,50 €</t>
         </is>
       </c>
-      <c r="B31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="16">
-        <f>B31*0.5</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="B37" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="39">
+        <f>B37*0.5</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>0,20 €</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="18">
-        <f>B32*0.2</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B38" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="41">
+        <f>B38*0.2</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="37" t="inlineStr">
         <is>
           <t>0,10 €</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="16">
-        <f>B33*0.1</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="B39" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="39">
+        <f>B39*0.1</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>0,05 €</t>
         </is>
       </c>
-      <c r="B34" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="18">
-        <f>B34*0.05</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B40" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="41">
+        <f>B40*0.05</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="37" t="inlineStr">
+        <is>
+          <t>0,02 €</t>
+        </is>
+      </c>
+      <c r="B41" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="39">
+        <f>B41*0.02</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>0,01 €</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="16">
-        <f>B35*0.01</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="B42" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="41">
+        <f>B42*0.01</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>TOTAL EFECTIVO</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n"/>
-      <c r="C36" s="21">
-        <f>SUM(C21:C35)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="21">
+        <f>SUM(C27:C42)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>📊 Resumen de Cierre</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="42" t="inlineStr">
         <is>
           <t>Importe (€)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Total Efectivo</t>
-        </is>
-      </c>
-      <c r="B40" s="16">
-        <f>C36</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Total Efectivo (recuento)</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="43">
+        <f>C43</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Fondo de caja inicial (−)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="43">
+        <f>IFERROR('Apertura de Caja'!C23,0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Ventas en efectivo (contado − fondo)</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="43">
+        <f>IFERROR(C47-C48,0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Total Tarjetas (Visa/MC)</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="B50" s="20" t="n"/>
+      <c r="C50" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Total Otros (Bizum, Vales)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="22" t="inlineStr">
+      <c r="B51" s="20" t="n"/>
+      <c r="C51" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>TOTAL FACTURADO</t>
         </is>
       </c>
-      <c r="B43" s="23">
-        <f>B40+B41+B42</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="B52" s="20" t="n"/>
+      <c r="C52" s="45">
+        <f>C49+C50+C51</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Z del TPV</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="22" t="inlineStr">
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>DESCUADRE</t>
         </is>
       </c>
-      <c r="B45" s="23">
-        <f>B43-B44</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="46"/>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="45">
+        <f>IFERROR(C52-C53,0)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>Firma del responsable: _________________________     Hora: ________</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A47:F47"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="20">
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D2:G2"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A48:B48"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:F16">
+  <conditionalFormatting sqref="A5:G21">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$D5="✓"</formula>
+      <formula>$E5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="D5 D6 D7 D8 D9 D10 D11 D12 D13 D14 D15 D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Selecciona ✓, ✗ o —" type="list">
-      <formula1>"✓,✗,—"</formula1>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="cellIs" priority="2" operator="notEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B27 B28 B29 B30 B31 B32 B33 B35 B36 B37 B38 B39 B40 B41 B42" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Cantidad no válida" error="Escribe el número de billetes o monedas: un número entero y positivo, sin decimales." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
@@ -1747,7 +2419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1758,7 +2430,8 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1794,7 +2467,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>Ventas Efectivo</t>
+          <t>Efectivo Contado</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -1814,15 +2487,20 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
+          <t>Z del TPV</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>Descuadre</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Depósito</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
@@ -1832,807 +2510,993 @@
       <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="16" t="n">
+      <c r="B5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="16">
-        <f>C5+D5+E5</f>
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="16" t="inlineStr"/>
-      <c r="H5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8" t="inlineStr"/>
+        <f>IF(SUM(C5:E5)=0,0,SUM(C5:E5)-B5)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16">
+        <f>IFERROR(F5-G5,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="32" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="B6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="18">
-        <f>C6+D6+E6</f>
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="18" t="inlineStr"/>
-      <c r="H6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10" t="inlineStr"/>
+        <f>IF(SUM(C6:E6)=0,0,SUM(C6:E6)-B6)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <f>IFERROR(F6-G6,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="32" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="16" t="n">
+      <c r="B7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="16">
-        <f>C7+D7+E7</f>
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8" t="inlineStr"/>
+        <f>IF(SUM(C7:E7)=0,0,SUM(C7:E7)-B7)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <f>IFERROR(F7-G7,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="32" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="B8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="18">
-        <f>C8+D8+E8</f>
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="18" t="inlineStr"/>
-      <c r="H8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
+        <f>IF(SUM(C8:E8)=0,0,SUM(C8:E8)-B8)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18">
+        <f>IFERROR(F8-G8,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="32" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="n">
+      <c r="B9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="16">
-        <f>C9+D9+E9</f>
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="16" t="inlineStr"/>
-      <c r="H9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr"/>
+        <f>IF(SUM(C9:E9)=0,0,SUM(C9:E9)-B9)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f>IFERROR(F9-G9,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="32" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="B10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="18">
-        <f>C10+D10+E10</f>
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="18" t="inlineStr"/>
-      <c r="H10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="10" t="inlineStr"/>
+        <f>IF(SUM(C10:E10)=0,0,SUM(C10:E10)-B10)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <f>IFERROR(F10-G10,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="32" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16" t="n">
+      <c r="B11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="16">
-        <f>C11+D11+E11</f>
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="16" t="inlineStr"/>
-      <c r="H11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="inlineStr"/>
+        <f>IF(SUM(C11:E11)=0,0,SUM(C11:E11)-B11)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <f>IFERROR(F11-G11,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="32" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="B12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="18">
-        <f>C12+D12+E12</f>
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="18" t="inlineStr"/>
-      <c r="H12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="10" t="inlineStr"/>
+        <f>IF(SUM(C12:E12)=0,0,SUM(C12:E12)-B12)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <f>IFERROR(F12-G12,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="32" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="B13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="16">
-        <f>C13+D13+E13</f>
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr"/>
+        <f>IF(SUM(C13:E13)=0,0,SUM(C13:E13)-B13)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f>IFERROR(F13-G13,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="B14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="18">
-        <f>C14+D14+E14</f>
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="18" t="inlineStr"/>
-      <c r="H14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="10" t="inlineStr"/>
+        <f>IF(SUM(C14:E14)=0,0,SUM(C14:E14)-B14)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <f>IFERROR(F14-G14,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I14" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="16" t="n">
+      <c r="B15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="16">
-        <f>C15+D15+E15</f>
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8" t="inlineStr"/>
+        <f>IF(SUM(C15:E15)=0,0,SUM(C15:E15)-B15)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="16">
+        <f>IFERROR(F15-G15,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="32" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="B16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="18">
-        <f>C16+D16+E16</f>
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="18" t="inlineStr"/>
-      <c r="H16" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="10" t="inlineStr"/>
+        <f>IF(SUM(C16:E16)=0,0,SUM(C16:E16)-B16)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <f>IFERROR(F16-G16,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="32" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="16" t="n">
+      <c r="B17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="16">
-        <f>C17+D17+E17</f>
-        <v>0.0</v>
-      </c>
-      <c r="G17" s="16" t="inlineStr"/>
-      <c r="H17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8" t="inlineStr"/>
+        <f>IF(SUM(C17:E17)=0,0,SUM(C17:E17)-B17)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="16">
+        <f>IFERROR(F17-G17,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="32" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="18" t="n">
+      <c r="B18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="18">
-        <f>C18+D18+E18</f>
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="18" t="inlineStr"/>
-      <c r="H18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10" t="inlineStr"/>
+        <f>IF(SUM(C18:E18)=0,0,SUM(C18:E18)-B18)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="18">
+        <f>IFERROR(F18-G18,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="32" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="16" t="n">
+      <c r="B19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="16">
-        <f>C19+D19+E19</f>
-        <v>0.0</v>
-      </c>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="8" t="inlineStr"/>
+        <f>IF(SUM(C19:E19)=0,0,SUM(C19:E19)-B19)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="16">
+        <f>IFERROR(F19-G19,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="32" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="B20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="18">
-        <f>C20+D20+E20</f>
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="18" t="inlineStr"/>
-      <c r="H20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="10" t="inlineStr"/>
+        <f>IF(SUM(C20:E20)=0,0,SUM(C20:E20)-B20)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18">
+        <f>IFERROR(F20-G20,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="32" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="16" t="n">
+      <c r="B21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="16">
-        <f>C21+D21+E21</f>
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr"/>
+        <f>IF(SUM(C21:E21)=0,0,SUM(C21:E21)-B21)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="16">
+        <f>IFERROR(F21-G21,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="32" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="18" t="n">
+      <c r="B22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="18">
-        <f>C22+D22+E22</f>
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="18" t="inlineStr"/>
-      <c r="H22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="10" t="inlineStr"/>
+        <f>IF(SUM(C22:E22)=0,0,SUM(C22:E22)-B22)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="18">
+        <f>IFERROR(F22-G22,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="32" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="16" t="n">
+      <c r="B23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="16">
-        <f>C23+D23+E23</f>
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="8" t="inlineStr"/>
+        <f>IF(SUM(C23:E23)=0,0,SUM(C23:E23)-B23)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="16">
+        <f>IFERROR(F23-G23,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="32" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="18" t="n">
+      <c r="B24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="18">
-        <f>C24+D24+E24</f>
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="18" t="inlineStr"/>
-      <c r="H24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="10" t="inlineStr"/>
+        <f>IF(SUM(C24:E24)=0,0,SUM(C24:E24)-B24)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="18">
+        <f>IFERROR(F24-G24,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="32" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="16" t="n">
+      <c r="B25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="16">
-        <f>C25+D25+E25</f>
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr"/>
+        <f>IF(SUM(C25:E25)=0,0,SUM(C25:E25)-B25)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="16">
+        <f>IFERROR(F25-G25,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="32" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="18" t="n">
+      <c r="B26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="18">
-        <f>C26+D26+E26</f>
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="18" t="inlineStr"/>
-      <c r="H26" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="inlineStr"/>
+        <f>IF(SUM(C26:E26)=0,0,SUM(C26:E26)-B26)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="18">
+        <f>IFERROR(F26-G26,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="32" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="16" t="n">
+      <c r="B27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="16">
-        <f>C27+D27+E27</f>
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="8" t="inlineStr"/>
+        <f>IF(SUM(C27:E27)=0,0,SUM(C27:E27)-B27)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="16">
+        <f>IFERROR(F27-G27,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="32" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18" t="n">
+      <c r="B28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="18">
-        <f>C28+D28+E28</f>
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="18" t="inlineStr"/>
-      <c r="H28" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10" t="inlineStr"/>
+        <f>IF(SUM(C28:E28)=0,0,SUM(C28:E28)-B28)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="18">
+        <f>IFERROR(F28-G28,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="32" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="16" t="n">
+      <c r="B29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="16">
-        <f>C29+D29+E29</f>
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="16" t="inlineStr"/>
-      <c r="H29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="8" t="inlineStr"/>
+        <f>IF(SUM(C29:E29)=0,0,SUM(C29:E29)-B29)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="16">
+        <f>IFERROR(F29-G29,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I29" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="32" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="17" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="18" t="n">
+      <c r="B30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="18">
-        <f>C30+D30+E30</f>
-        <v>0.0</v>
-      </c>
-      <c r="G30" s="18" t="inlineStr"/>
-      <c r="H30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="10" t="inlineStr"/>
+        <f>IF(SUM(C30:E30)=0,0,SUM(C30:E30)-B30)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="18">
+        <f>IFERROR(F30-G30,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I30" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="32" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="16" t="n">
+      <c r="B31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="16">
-        <f>C31+D31+E31</f>
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="16" t="inlineStr"/>
-      <c r="H31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="8" t="inlineStr"/>
+        <f>IF(SUM(C31:E31)=0,0,SUM(C31:E31)-B31)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="16">
+        <f>IFERROR(F31-G31,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I31" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="32" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="18" t="n">
+      <c r="B32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="18">
-        <f>C32+D32+E32</f>
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="18" t="inlineStr"/>
-      <c r="H32" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10" t="inlineStr"/>
+        <f>IF(SUM(C32:E32)=0,0,SUM(C32:E32)-B32)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="18">
+        <f>IFERROR(F32-G32,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="32" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="16" t="n">
+      <c r="B33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="16">
-        <f>C33+D33+E33</f>
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="16" t="inlineStr"/>
-      <c r="H33" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="8" t="inlineStr"/>
+        <f>IF(SUM(C33:E33)=0,0,SUM(C33:E33)-B33)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="16">
+        <f>IFERROR(F33-G33,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="32" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="17" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="18" t="n">
+      <c r="B34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="18">
-        <f>C34+D34+E34</f>
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="18" t="inlineStr"/>
-      <c r="H34" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10" t="inlineStr"/>
+        <f>IF(SUM(C34:E34)=0,0,SUM(C34:E34)-B34)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(F34-G34,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="32" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="16" t="n">
+      <c r="B35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="46" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="16">
-        <f>C35+D35+E35</f>
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="16" t="inlineStr"/>
-      <c r="H35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="8" t="inlineStr"/>
+        <f>IF(SUM(C35:E35)=0,0,SUM(C35:E35)-B35)</f>
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="16">
+        <f>IFERROR(F35-G35,0)</f>
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="32" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="19" t="inlineStr">
@@ -2641,7 +3505,7 @@
         </is>
       </c>
       <c r="B36" s="24">
-        <f>SUM(B5:B35)</f>
+        <f>IFERROR(AVERAGEIF(B5:B35,"&gt;0"),0)</f>
         <v>0.0</v>
       </c>
       <c r="C36" s="24">
@@ -2665,26 +3529,43 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="24">
-        <f>SUM(H5:H35)</f>
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="19" t="inlineStr"/>
-    </row>
-    <row r="37"/>
+        <f>SUMIF(H5:H35,"&gt;0")-SUMIF(H5:H35,"&lt;0")</f>
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="24">
+        <f>SUM(I5:I35)</f>
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="19" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="47" t="inlineStr">
+        <is>
+          <t>«Efectivo Contado» es el recuento del cajón TAL CUAL, con el fondo dentro: el Total Facturado ya lo descuenta. En TOTALES, «Fondo Apertura» es el fondo MEDIO de los días anotados (un saldo no se suma) y «Descuadre» es el descuadre ACUMULADO en valor absoluto: un +50 y un −50 son 100 € de descuadre, no 0.</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>© AI Chef Pro — aichef.pro</t>
+          <t>— Kit de Tareas Recurrentes · Dark Kitchen · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="A1:I1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
+  <mergeCells count="5">
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <conditionalFormatting sqref="H5:H35">
+    <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
